--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>117</v>
       </c>
       <c r="T5" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>98</v>
       </c>
       <c r="T7" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>128</v>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
         <v>7</v>
@@ -3271,10 +3271,10 @@
         <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T16" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
@@ -3319,6 +3319,7 @@
 Tallbit
 Havsörn
 Kungsfågel
+Törnskata
 Huggorm
 Vanlig padda
 Fläcknycklar
@@ -3372,10 +3373,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3503,10 +3504,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3628,10 +3629,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3744,10 +3745,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3861,10 +3862,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3974,10 +3975,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4074,10 +4075,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
@@ -879,16 +879,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
@@ -915,6 +915,7 @@
 Ramaria ossolana
 Ringlav
 Rotfingersvamp
+Ryl
 Silverblåvinge
 Skrovlig taggsvamp
 Starrgräsfjäril
@@ -1091,10 +1092,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1311,10 +1312,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1528,10 +1529,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1736,10 +1737,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1934,10 +1935,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2110,10 +2111,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2280,10 +2281,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2444,10 +2445,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2607,10 +2608,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2769,10 +2770,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2922,10 +2923,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3076,10 +3077,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3225,10 +3226,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3373,10 +3374,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3504,10 +3505,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3629,10 +3630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3745,10 +3746,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3862,10 +3863,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3975,10 +3976,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4075,10 +4076,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -542,30 +542,35 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Geotifflänk</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -583,10 +588,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -803,26 +808,30 @@
         <v/>
       </c>
       <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Ramsjöns naturreservat georefererad karta.tif", "Ramsjöns naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Ramsjöns naturreservat karta knärot.png", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Ramsjöns naturreservat FSC-klagomål.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Ramsjöns naturreservat FSC-klagomål mail.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Ramsjöns naturreservat tillsynsbegäran.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Ramsjöns naturreservat tillsynsbegäran mail.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Ramsjöns naturreservat prioriterade fågelarter.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
@@ -839,10 +848,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1056,26 +1065,30 @@
         <v/>
       </c>
       <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Högstaskogens naturreservat georefererad karta.tif", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Högstaskogens naturreservat karta knärot.png", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Högstaskogens naturreservat FSC-klagomål.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Högstaskogens naturreservat FSC-klagomål mail.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Högstaskogens naturreservat tillsynsbegäran.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Högstaskogens naturreservat tillsynsbegäran mail.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Högstaskogens naturreservat prioriterade fågelarter.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
@@ -1092,10 +1105,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1276,26 +1289,30 @@
         <v/>
       </c>
       <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Ornös nordspets georefererad karta.tif", "Ornös nordspets")</f>
+        <v/>
+      </c>
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Ornös nordspets karta knärot.png", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Ornös nordspets FSC-klagomål.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Ornös nordspets FSC-klagomål mail.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Ornös nordspets tillsynsbegäran.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Ornös nordspets tillsynsbegäran mail.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Ornös nordspets prioriterade fågelarter.docx", "Ornös nordspets")</f>
         <v/>
       </c>
@@ -1312,10 +1329,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1493,26 +1510,30 @@
         <v/>
       </c>
       <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat utökat georefererad karta.tif", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat utökat karta knärot.png", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat utökat FSC-klagomål.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat utökat FSC-klagomål mail.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat utökat tillsynsbegäran.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat utökat tillsynsbegäran mail.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat utökat prioriterade fågelarter.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
@@ -1529,10 +1550,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1704,23 +1725,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Skäggsmoskogens naturreservat karta.png", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Skäggsmoskogens naturreservat georefererad karta.tif", "Skäggsmoskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Skäggsmoskogens naturreservat FSC-klagomål.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Skäggsmoskogens naturreservat FSC-klagomål mail.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Skäggsmoskogens naturreservat tillsynsbegäran.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Skäggsmoskogens naturreservat tillsynsbegäran mail.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Skäggsmoskogens naturreservat prioriterade fågelarter.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
@@ -1737,10 +1762,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1899,26 +1924,30 @@
         <v/>
       </c>
       <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat georefererad karta.tif", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat karta knärot.png", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat FSC-klagomål.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat FSC-klagomål mail.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat tillsynsbegäran.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat tillsynsbegäran mail.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat prioriterade fågelarter.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
@@ -1935,10 +1964,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2075,26 +2104,30 @@
         <v/>
       </c>
       <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Breviksnäs georefererad karta.tif", "Breviksnäs")</f>
+        <v/>
+      </c>
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Breviksnäs karta knärot.png", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Breviksnäs FSC-klagomål.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Breviksnäs FSC-klagomål mail.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Breviksnäs tillsynsbegäran.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Breviksnäs tillsynsbegäran mail.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Breviksnäs prioriterade fågelarter.docx", "Breviksnäs")</f>
         <v/>
       </c>
@@ -2111,10 +2144,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2245,26 +2278,30 @@
         <v/>
       </c>
       <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tyresta naturreservat med skogsbruk georefererad karta.tif", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tyresta naturreservat med skogsbruk karta knärot.png", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tyresta naturreservat med skogsbruk FSC-klagomål.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tyresta naturreservat med skogsbruk FSC-klagomål mail.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tyresta naturreservat med skogsbruk tillsynsbegäran.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tyresta naturreservat med skogsbruk tillsynsbegäran mail.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tyresta naturreservat med skogsbruk prioriterade fågelarter.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
@@ -2281,10 +2318,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2412,23 +2449,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norra skogen karta.png", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norra skogen georefererad karta.tif", "Norra skogen")</f>
+        <v/>
+      </c>
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norra skogen FSC-klagomål.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norra skogen FSC-klagomål mail.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norra skogen tillsynsbegäran.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norra skogen tillsynsbegäran mail.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norra skogen prioriterade fågelarter.docx", "Norra skogen")</f>
         <v/>
       </c>
@@ -2445,10 +2486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2575,23 +2616,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
@@ -2608,10 +2653,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2737,23 +2782,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Örans naturreservat karta.png", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Örans naturreservat georefererad karta.tif", "Örans naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Örans naturreservat FSC-klagomål.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Örans naturreservat FSC-klagomål mail.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Örans naturreservat tillsynsbegäran.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Örans naturreservat tillsynsbegäran mail.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Örans naturreservat prioriterade fågelarter.docx", "Örans naturreservat")</f>
         <v/>
       </c>
@@ -2770,10 +2819,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2890,23 +2939,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbyskogens naturreservat karta.png", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbyskogens naturreservat georefererad karta.tif", "Norrbyskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbyskogens naturreservat FSC-klagomål.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbyskogens naturreservat FSC-klagomål mail.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbyskogens naturreservat tillsynsbegäran.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbyskogens naturreservat tillsynsbegäran mail.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbyskogens naturreservat prioriterade fågelarter.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
@@ -2923,10 +2976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3041,26 +3094,30 @@
         <v/>
       </c>
       <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norr om Norra skogens naturreservat georefererad karta.tif", "Norr om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norr om Norra skogens naturreservat karta knärot.png", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norr om Norra skogens naturreservat FSC-klagomål.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norr om Norra skogens naturreservat FSC-klagomål mail.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norr om Norra skogens naturreservat tillsynsbegäran.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norr om Norra skogens naturreservat tillsynsbegäran mail.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norr om Norra skogens naturreservat prioriterade fågelarter.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
@@ -3077,10 +3134,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3190,26 +3247,30 @@
         <v/>
       </c>
       <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tutvikskogens naturreservat georefererad karta.tif", "Tutvikskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tutvikskogens naturreservat karta knärot.png", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tutvikskogens naturreservat FSC-klagomål.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tutvikskogens naturreservat FSC-klagomål mail.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tutvikskogens naturreservat tillsynsbegäran.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tutvikskogens naturreservat tillsynsbegäran mail.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tutvikskogens naturreservat prioriterade fågelarter.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
@@ -3226,10 +3287,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3338,26 +3399,30 @@
         <v/>
       </c>
       <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat söder georefererad karta.tif", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat söder karta knärot.png", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat söder FSC-klagomål.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat söder FSC-klagomål mail.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat söder tillsynsbegäran.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat söder tillsynsbegäran mail.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat söder prioriterade fågelarter.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
@@ -3374,10 +3439,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3476,19 +3541,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Kapellöns naturreservat karta.png", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Kapellöns naturreservat georefererad karta.tif", "Kapellöns naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Kapellöns naturreservat FSC-klagomål.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Kapellöns naturreservat FSC-klagomål mail.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Kapellöns naturreservat tillsynsbegäran.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Kapellöns naturreservat tillsynsbegäran mail.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
@@ -3505,10 +3574,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3597,23 +3666,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Söderbyskogens naturreservat karta.png", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Söderbyskogens naturreservat georefererad karta.tif", "Söderbyskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Söderbyskogens naturreservat FSC-klagomål.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Söderbyskogens naturreservat FSC-klagomål mail.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Söderbyskogens naturreservat tillsynsbegäran.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Söderbyskogens naturreservat tillsynsbegäran mail.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Söderbyskogens naturreservat prioriterade fågelarter.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
@@ -3630,10 +3703,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3717,19 +3790,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Jordbro naturreservat karta.png", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Jordbro naturreservat georefererad karta.tif", "Jordbro naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Jordbro naturreservat FSC-klagomål.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Jordbro naturreservat FSC-klagomål mail.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Jordbro naturreservat tillsynsbegäran.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Jordbro naturreservat tillsynsbegäran mail.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
@@ -3746,10 +3823,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3827,26 +3904,30 @@
         <v/>
       </c>
       <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Bockbergets naturreservat georefererad karta.tif", "Bockbergets naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Bockbergets naturreservat karta knärot.png", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Bockbergets naturreservat FSC-klagomål.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Bockbergets naturreservat FSC-klagomål mail.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Bockbergets naturreservat tillsynsbegäran.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Bockbergets naturreservat tillsynsbegäran mail.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Bockbergets naturreservat prioriterade fågelarter.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
@@ -3863,10 +3944,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3943,23 +4024,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Jordbro gravfälts naturreservat karta.png", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Jordbro gravfälts naturreservat georefererad karta.tif", "Jordbro gravfälts naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Jordbro gravfälts naturreservat FSC-klagomål.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Jordbro gravfälts naturreservat FSC-klagomål mail.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Jordbro gravfälts naturreservat tillsynsbegäran.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Jordbro gravfälts naturreservat tillsynsbegäran mail.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Jordbro gravfälts naturreservat prioriterade fågelarter.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
@@ -3976,10 +4061,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4043,23 +4128,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Öster om Norra skogens naturreservat karta.png", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Öster om Norra skogens naturreservat georefererad karta.tif", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Öster om Norra skogens naturreservat FSC-klagomål.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Öster om Norra skogens naturreservat FSC-klagomål mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Öster om Norra skogens naturreservat tillsynsbegäran.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Öster om Norra skogens naturreservat tillsynsbegäran mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Öster om Norra skogens naturreservat prioriterade fågelarter.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
@@ -4076,10 +4165,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4147,19 +4236,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -522,55 +522,60 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Antal fynd</t>
+          <t>Fynd</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Nya fynd</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>Artnamn</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Artfyndslänk</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Kartlänk</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Geotifflänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -588,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -639,7 +644,10 @@
       <c r="T2" t="n">
         <v>778</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Klätt
 Koppartaggsvamp
@@ -799,39 +807,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V2">
+      <c r="W2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Ramsjöns naturreservat artfynd.xlsx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="W2">
+      <c r="X2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Ramsjöns naturreservat karta.png", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Ramsjöns naturreservat georefererad karta.tif", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Ramsjöns naturreservat karta knärot.png", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Ramsjöns naturreservat FSC-klagomål.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Ramsjöns naturreservat FSC-klagomål mail.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Ramsjöns naturreservat tillsynsbegäran.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Ramsjöns naturreservat tillsynsbegäran mail.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Ramsjöns naturreservat prioriterade fågelarter.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
@@ -848,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,9 +905,12 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1242</v>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+        <v>1243</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Ask
 Brödtaggsvamp
@@ -1056,39 +1067,39 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="V3">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Högstaskogens naturreservat artfynd.xlsx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W3">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Högstaskogens naturreservat karta.png", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Högstaskogens naturreservat georefererad karta.tif", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Högstaskogens naturreservat karta knärot.png", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Högstaskogens naturreservat FSC-klagomål.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Högstaskogens naturreservat FSC-klagomål mail.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Högstaskogens naturreservat tillsynsbegäran.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Högstaskogens naturreservat tillsynsbegäran mail.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Högstaskogens naturreservat prioriterade fågelarter.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
@@ -1105,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1156,7 +1167,10 @@
       <c r="T4" t="n">
         <v>443</v>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Almlav
 Ask
@@ -1280,39 +1294,39 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="V4">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Ornös nordspets artfynd.xlsx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="W4">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Ornös nordspets karta.png", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Ornös nordspets georefererad karta.tif", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Ornös nordspets karta knärot.png", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Ornös nordspets FSC-klagomål.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Ornös nordspets FSC-klagomål mail.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Ornös nordspets tillsynsbegäran.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Ornös nordspets tillsynsbegäran mail.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Ornös nordspets prioriterade fågelarter.docx", "Ornös nordspets")</f>
         <v/>
       </c>
@@ -1329,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1380,7 +1394,10 @@
       <c r="T5" t="n">
         <v>819</v>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Brödtaggsvamp
 Koppartaggsvamp
@@ -1501,39 +1518,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V5">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat utökat artfynd.xlsx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="W5">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat utökat karta.png", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat utökat georefererad karta.tif", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat utökat karta knärot.png", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat utökat FSC-klagomål.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat utökat FSC-klagomål mail.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat utökat tillsynsbegäran.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat utökat tillsynsbegäran mail.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat utökat prioriterade fågelarter.docx", "Norrbytorps naturreservat utökat")</f>
         <v/>
       </c>
@@ -1550,10 +1567,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1606,7 +1623,10 @@
       <c r="T6" t="n">
         <v>265</v>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grusnejlika
 Havstrut
@@ -1717,35 +1737,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V6">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W6">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Skäggsmoskogens naturreservat karta.png", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Skäggsmoskogens naturreservat georefererad karta.tif", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Skäggsmoskogens naturreservat FSC-klagomål.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Skäggsmoskogens naturreservat FSC-klagomål mail.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Skäggsmoskogens naturreservat tillsynsbegäran.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Skäggsmoskogens naturreservat tillsynsbegäran mail.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Skäggsmoskogens naturreservat prioriterade fågelarter.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
@@ -1762,10 +1782,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1813,7 +1833,10 @@
       <c r="T7" t="n">
         <v>677</v>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Brödtaggsvamp
 Koppartaggsvamp
@@ -1915,39 +1938,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V7">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat artfynd.xlsx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="W7">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat karta.png", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat georefererad karta.tif", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat karta knärot.png", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat FSC-klagomål.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat FSC-klagomål mail.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat tillsynsbegäran.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat tillsynsbegäran mail.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat prioriterade fågelarter.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
@@ -1964,10 +1987,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2015,7 +2038,10 @@
       <c r="T8" t="n">
         <v>364</v>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Grönfink
@@ -2095,39 +2121,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V8">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Breviksnäs artfynd.xlsx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="W8">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Breviksnäs karta.png", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Breviksnäs georefererad karta.tif", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Breviksnäs karta knärot.png", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Breviksnäs FSC-klagomål.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Breviksnäs FSC-klagomål mail.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Breviksnäs tillsynsbegäran.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Breviksnäs tillsynsbegäran mail.docx", "Breviksnäs")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Breviksnäs prioriterade fågelarter.docx", "Breviksnäs")</f>
         <v/>
       </c>
@@ -2144,10 +2170,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2195,7 +2221,10 @@
       <c r="T9" t="n">
         <v>530</v>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Brandnäva
 Koppartaggsvamp
@@ -2269,39 +2298,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V9">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="W9">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Tyresta naturreservat med skogsbruk karta.png", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tyresta naturreservat med skogsbruk georefererad karta.tif", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tyresta naturreservat med skogsbruk karta knärot.png", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tyresta naturreservat med skogsbruk FSC-klagomål.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tyresta naturreservat med skogsbruk FSC-klagomål mail.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tyresta naturreservat med skogsbruk tillsynsbegäran.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tyresta naturreservat med skogsbruk tillsynsbegäran mail.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tyresta naturreservat med skogsbruk prioriterade fågelarter.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
@@ -2318,10 +2347,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2369,7 +2398,10 @@
       <c r="T10" t="n">
         <v>423</v>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ejder
 Grangråticka
@@ -2441,35 +2473,35 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="V10">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norra skogen artfynd.xlsx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="W10">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norra skogen karta.png", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norra skogen georefererad karta.tif", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norra skogen FSC-klagomål.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norra skogen FSC-klagomål mail.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norra skogen tillsynsbegäran.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norra skogen tillsynsbegäran mail.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norra skogen prioriterade fågelarter.docx", "Norra skogen")</f>
         <v/>
       </c>
@@ -2486,10 +2518,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2537,7 +2569,10 @@
       <c r="T11" t="n">
         <v>781</v>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knölig taggsvamp
 Koppartaggsvamp
@@ -2608,35 +2643,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V11">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Lervassa träsk naturreservat artfynd.xlsx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="W11">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
@@ -2653,10 +2688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2704,7 +2739,10 @@
       <c r="T12" t="n">
         <v>111</v>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Brunfläckig pärlemorfjäril
 Garnlav
@@ -2774,35 +2812,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V12">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Örans naturreservat artfynd.xlsx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="W12">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Örans naturreservat karta.png", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Örans naturreservat georefererad karta.tif", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Örans naturreservat FSC-klagomål.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Örans naturreservat FSC-klagomål mail.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Örans naturreservat tillsynsbegäran.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Örans naturreservat tillsynsbegäran mail.docx", "Örans naturreservat")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Örans naturreservat prioriterade fågelarter.docx", "Örans naturreservat")</f>
         <v/>
       </c>
@@ -2819,10 +2857,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2870,7 +2908,10 @@
       <c r="T13" t="n">
         <v>169</v>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Fläckfingersvamp
 Gränsticka
@@ -2931,35 +2972,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V13">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbyskogens naturreservat artfynd.xlsx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W13">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbyskogens naturreservat karta.png", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbyskogens naturreservat georefererad karta.tif", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbyskogens naturreservat FSC-klagomål.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbyskogens naturreservat FSC-klagomål mail.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbyskogens naturreservat tillsynsbegäran.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbyskogens naturreservat tillsynsbegäran mail.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbyskogens naturreservat prioriterade fågelarter.docx", "Norrbyskogens naturreservat")</f>
         <v/>
       </c>
@@ -2976,10 +3017,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3027,7 +3068,10 @@
       <c r="T14" t="n">
         <v>230</v>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dofttaggsvamp
@@ -3085,39 +3129,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V14">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norr om Norra skogens naturreservat artfynd.xlsx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W14">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norr om Norra skogens naturreservat karta.png", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norr om Norra skogens naturreservat georefererad karta.tif", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norr om Norra skogens naturreservat karta knärot.png", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norr om Norra skogens naturreservat FSC-klagomål.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norr om Norra skogens naturreservat FSC-klagomål mail.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norr om Norra skogens naturreservat tillsynsbegäran.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norr om Norra skogens naturreservat tillsynsbegäran mail.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norr om Norra skogens naturreservat prioriterade fågelarter.docx", "Norr om Norra skogens naturreservat")</f>
         <v/>
       </c>
@@ -3134,10 +3178,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3185,7 +3229,10 @@
       <c r="T15" t="n">
         <v>352</v>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Goliatmusseron
@@ -3238,39 +3285,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V15">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Tutvikskogens naturreservat artfynd.xlsx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W15">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Tutvikskogens naturreservat karta.png", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tutvikskogens naturreservat georefererad karta.tif", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tutvikskogens naturreservat karta knärot.png", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tutvikskogens naturreservat FSC-klagomål.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tutvikskogens naturreservat FSC-klagomål mail.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tutvikskogens naturreservat tillsynsbegäran.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tutvikskogens naturreservat tillsynsbegäran mail.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tutvikskogens naturreservat prioriterade fågelarter.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
@@ -3287,10 +3334,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3338,7 +3385,10 @@
       <c r="T16" t="n">
         <v>280</v>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Hornuggla
 Brunfläckig pärlemorfjäril
@@ -3390,39 +3440,39 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="V16">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat söder artfynd.xlsx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="W16">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat söder karta.png", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat söder georefererad karta.tif", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat söder karta knärot.png", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat söder FSC-klagomål.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat söder FSC-klagomål mail.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat söder tillsynsbegäran.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat söder tillsynsbegäran mail.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat söder prioriterade fågelarter.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
@@ -3439,10 +3489,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3495,7 +3545,10 @@
       <c r="T17" t="n">
         <v>68</v>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Gullklöver
@@ -3533,31 +3586,31 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="V17">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Kapellöns naturreservat artfynd.xlsx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="W17">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Kapellöns naturreservat karta.png", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Kapellöns naturreservat georefererad karta.tif", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Kapellöns naturreservat FSC-klagomål.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Kapellöns naturreservat FSC-klagomål mail.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Kapellöns naturreservat tillsynsbegäran.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Kapellöns naturreservat tillsynsbegäran mail.docx", "Kapellöns naturreservat")</f>
         <v/>
       </c>
@@ -3574,10 +3627,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3630,7 +3683,10 @@
       <c r="T18" t="n">
         <v>93</v>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Jungfrulin
@@ -3658,35 +3714,35 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="V18">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Söderbyskogens naturreservat artfynd.xlsx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W18">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Söderbyskogens naturreservat karta.png", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Söderbyskogens naturreservat georefererad karta.tif", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Söderbyskogens naturreservat FSC-klagomål.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Söderbyskogens naturreservat FSC-klagomål mail.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Söderbyskogens naturreservat tillsynsbegäran.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Söderbyskogens naturreservat tillsynsbegäran mail.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Söderbyskogens naturreservat prioriterade fågelarter.docx", "Söderbyskogens naturreservat")</f>
         <v/>
       </c>
@@ -3703,10 +3759,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3759,7 +3815,10 @@
       <c r="T19" t="n">
         <v>23</v>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Igelkott
@@ -3782,31 +3841,31 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="V19">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Jordbro naturreservat artfynd.xlsx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="W19">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Jordbro naturreservat karta.png", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Jordbro naturreservat georefererad karta.tif", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Jordbro naturreservat FSC-klagomål.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Jordbro naturreservat FSC-klagomål mail.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Jordbro naturreservat tillsynsbegäran.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Jordbro naturreservat tillsynsbegäran mail.docx", "Jordbro naturreservat")</f>
         <v/>
       </c>
@@ -3823,10 +3882,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3879,7 +3938,10 @@
       <c r="T20" t="n">
         <v>20</v>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Knärot
@@ -3895,39 +3957,39 @@
 Salskrake</t>
         </is>
       </c>
-      <c r="V20">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Bockbergets naturreservat artfynd.xlsx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="W20">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Bockbergets naturreservat karta.png", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Bockbergets naturreservat georefererad karta.tif", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Bockbergets naturreservat karta knärot.png", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Bockbergets naturreservat FSC-klagomål.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Bockbergets naturreservat FSC-klagomål mail.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Bockbergets naturreservat tillsynsbegäran.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Bockbergets naturreservat tillsynsbegäran mail.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Bockbergets naturreservat prioriterade fågelarter.docx", "Bockbergets naturreservat")</f>
         <v/>
       </c>
@@ -3944,10 +4006,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4000,7 +4062,10 @@
       <c r="T21" t="n">
         <v>13</v>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Nötkråka
@@ -4016,35 +4081,35 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V21">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Jordbro gravfälts naturreservat artfynd.xlsx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="W21">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Jordbro gravfälts naturreservat karta.png", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Jordbro gravfälts naturreservat georefererad karta.tif", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Jordbro gravfälts naturreservat FSC-klagomål.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Jordbro gravfälts naturreservat FSC-klagomål mail.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Jordbro gravfälts naturreservat tillsynsbegäran.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Jordbro gravfälts naturreservat tillsynsbegäran mail.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Jordbro gravfälts naturreservat prioriterade fågelarter.docx", "Jordbro gravfälts naturreservat")</f>
         <v/>
       </c>
@@ -4061,10 +4126,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4112,7 +4177,10 @@
       <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Nästrot
@@ -4120,35 +4188,35 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="V22">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="W22">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Öster om Norra skogens naturreservat karta.png", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Öster om Norra skogens naturreservat georefererad karta.tif", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Öster om Norra skogens naturreservat FSC-klagomål.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Öster om Norra skogens naturreservat FSC-klagomål mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Öster om Norra skogens naturreservat tillsynsbegäran.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Öster om Norra skogens naturreservat tillsynsbegäran mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Öster om Norra skogens naturreservat prioriterade fågelarter.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
@@ -4165,10 +4233,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4221,38 +4289,41 @@
       <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Adam och eva
 Solvända
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="V23">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="W23">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         <v>21</v>
       </c>
       <c r="S5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T5" t="n">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1499,6 +1499,7 @@
 Mattlummer
 Nattskärra
 Spillkråka
+Tallört (aggregat)
 Tjäder
 Gröngöling
 Grönsiska
@@ -1567,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1782,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1828,10 +1829,10 @@
         <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1922,6 +1923,7 @@
 Mattlummer
 Nattskärra
 Spillkråka
+Tallört (aggregat)
 Tjäder
 Gröngöling
 Havsörn
@@ -1987,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2170,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2347,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2518,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2688,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2857,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3017,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3178,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3334,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3489,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3627,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3759,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3882,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4006,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4126,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4233,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>118</v>
       </c>
       <c r="T5" t="n">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>48</v>
       </c>
       <c r="T16" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>118</v>
       </c>
       <c r="T5" t="n">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1243</v>
+        <v>1254</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>194.4</v>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
         <v>31</v>
@@ -1389,10 +1389,10 @@
         <v>21</v>
       </c>
       <c r="S5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T5" t="n">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1501,6 +1501,7 @@
 Spillkråka
 Tallört (aggregat)
 Tjäder
+Tofsmes
 Gröngöling
 Grönsiska
 Havsörn
@@ -1568,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1783,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1832,7 +1833,7 @@
         <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1989,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2172,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2221,7 +2222,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2349,10 +2350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2520,10 +2521,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2690,10 +2691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2859,10 +2860,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3019,10 +3020,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3180,10 +3181,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3336,10 +3337,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3492,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3630,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3762,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3885,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4009,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4129,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4235,10 +4236,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Öster om Norra skogens naturreservat</t>
+          <t>Grytholmens naturreservat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4144,46 +4144,157 @@
           <t>Haninge</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>102.1</v>
+        <v>33</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Adam och eva
+Jungfrulin
+Solvända
+Sårläka
+Skogsknipprot
+Grönvit nattviol
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Öster om Norra skogens naturreservat</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>5</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Nästrot
@@ -4191,143 +4302,36 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Öster om Norra skogens naturreservat karta.png", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Öster om Norra skogens naturreservat georefererad karta.tif", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Öster om Norra skogens naturreservat FSC-klagomål.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Öster om Norra skogens naturreservat FSC-klagomål mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Öster om Norra skogens naturreservat tillsynsbegäran.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Öster om Norra skogens naturreservat tillsynsbegäran mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Öster om Norra skogens naturreservat prioriterade fågelarter.docx", "Öster om Norra skogens naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Grytholmens naturreservat</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>33</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva
-Solvända
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
@@ -896,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T3" t="n">
-        <v>1265</v>
+        <v>1227</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -935,7 +935,6 @@
 Ramaria ossolana
 Ringlav
 Rotfingersvamp
-Ryl
 Silverblåvinge
 Skrovlig taggsvamp
 Starrgräsfjäril
@@ -1116,10 +1115,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1164,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1342,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1362,7 +1361,7 @@
         <v>194.4</v>
       </c>
       <c r="J5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
         <v>31</v>
@@ -1389,10 +1388,10 @@
         <v>21</v>
       </c>
       <c r="S5" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T5" t="n">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1499,9 +1498,7 @@
 Mattlummer
 Nattskärra
 Spillkråka
-Tallört (aggregat)
 Tjäder
-Tofsmes
 Gröngöling
 Grönsiska
 Havsörn
@@ -1569,10 +1566,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1781,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1830,10 +1827,10 @@
         <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T7" t="n">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1924,7 +1921,6 @@
 Mattlummer
 Nattskärra
 Spillkråka
-Tallört (aggregat)
 Tjäder
 Gröngöling
 Havsörn
@@ -1990,10 +1986,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2169,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2222,7 +2218,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2350,10 +2346,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2521,10 +2517,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2691,10 +2687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2860,10 +2856,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3020,10 +3016,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3181,10 +3177,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3337,10 +3333,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3356,7 +3352,7 @@
         <v>128</v>
       </c>
       <c r="J16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
         <v>7</v>
@@ -3383,10 +3379,10 @@
         <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T16" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3434,7 +3430,6 @@
 Tallbit
 Havsörn
 Kungsfågel
-Törnskata
 Huggorm
 Vanlig padda
 Fläcknycklar
@@ -3492,10 +3487,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3630,10 +3625,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3762,10 +3757,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3885,10 +3880,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4009,10 +4004,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4120,7 +4115,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Grytholmens naturreservat</t>
+          <t>Öster om Norra skogens naturreservat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4129,10 +4124,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4144,157 +4139,46 @@
           <t>Haninge</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>33</v>
+        <v>102.1</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7</v>
-      </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva
-Jungfrulin
-Solvända
-Sårläka
-Skogsknipprot
-Grönvit nattviol
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Öster om Norra skogens naturreservat</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>102.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Nästrot
@@ -4302,36 +4186,143 @@
 Fläcknycklar</t>
         </is>
       </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Öster om Norra skogens naturreservat karta.png", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Öster om Norra skogens naturreservat georefererad karta.tif", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Öster om Norra skogens naturreservat FSC-klagomål.docx", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Öster om Norra skogens naturreservat FSC-klagomål mail.docx", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Öster om Norra skogens naturreservat tillsynsbegäran.docx", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Öster om Norra skogens naturreservat tillsynsbegäran mail.docx", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Öster om Norra skogens naturreservat prioriterade fågelarter.docx", "Öster om Norra skogens naturreservat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Grytholmens naturreservat</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Adam och eva
+Solvända
+Grönvit nattviol</t>
+        </is>
+      </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Öster om Norra skogens naturreservat karta.png", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Öster om Norra skogens naturreservat georefererad karta.tif", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Öster om Norra skogens naturreservat FSC-klagomål.docx", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Öster om Norra skogens naturreservat FSC-klagomål mail.docx", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Öster om Norra skogens naturreservat tillsynsbegäran.docx", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Öster om Norra skogens naturreservat tillsynsbegäran mail.docx", "Öster om Norra skogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Öster om Norra skogens naturreservat prioriterade fågelarter.docx", "Öster om Norra skogens naturreservat")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
@@ -896,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1227</v>
+        <v>1266</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -935,6 +935,7 @@
 Ramaria ossolana
 Ringlav
 Rotfingersvamp
+Ryl
 Silverblåvinge
 Skrovlig taggsvamp
 Starrgräsfjäril
@@ -1115,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1164,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1342,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1361,7 +1362,7 @@
         <v>194.4</v>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
         <v>31</v>
@@ -1388,10 +1389,10 @@
         <v>21</v>
       </c>
       <c r="S5" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="T5" t="n">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1498,7 +1499,9 @@
 Mattlummer
 Nattskärra
 Spillkråka
+Tallört (aggregat)
 Tjäder
+Tofsmes
 Gröngöling
 Grönsiska
 Havsörn
@@ -1566,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1781,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1827,10 +1830,10 @@
         <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1921,6 +1924,7 @@
 Mattlummer
 Nattskärra
 Spillkråka
+Tallört (aggregat)
 Tjäder
 Gröngöling
 Havsörn
@@ -1986,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2169,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2218,7 +2222,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2346,10 +2350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2517,10 +2521,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2687,10 +2691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2856,10 +2860,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3016,10 +3020,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3177,10 +3181,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3333,10 +3337,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3382,7 +3386,7 @@
         <v>47</v>
       </c>
       <c r="T16" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3487,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3625,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3757,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3880,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4004,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4115,7 +4119,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Öster om Norra skogens naturreservat</t>
+          <t>Grytholmens naturreservat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4124,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4139,46 +4143,157 @@
           <t>Haninge</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>102.1</v>
+        <v>33</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Adam och eva
+Jungfrulin
+Solvända
+Sårläka
+Skogsknipprot
+Grönvit nattviol
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Öster om Norra skogens naturreservat</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>5</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Nästrot
@@ -4186,143 +4301,36 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Öster om Norra skogens naturreservat artfynd.xlsx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Öster om Norra skogens naturreservat karta.png", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Öster om Norra skogens naturreservat georefererad karta.tif", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Öster om Norra skogens naturreservat FSC-klagomål.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Öster om Norra skogens naturreservat FSC-klagomål mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Öster om Norra skogens naturreservat tillsynsbegäran.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Öster om Norra skogens naturreservat tillsynsbegäran mail.docx", "Öster om Norra skogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Öster om Norra skogens naturreservat prioriterade fågelarter.docx", "Öster om Norra skogens naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Grytholmens naturreservat</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>33</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva
-Solvända
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Grytholmens naturreservat artfynd.xlsx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Grytholmens naturreservat karta.png", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Grytholmens naturreservat georefererad karta.tif", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Grytholmens naturreservat FSC-klagomål.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Grytholmens naturreservat FSC-klagomål mail.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Grytholmens naturreservat tillsynsbegäran.docx", "Grytholmens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Grytholmens naturreservat tillsynsbegäran mail.docx", "Grytholmens naturreservat")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>119</v>
       </c>
       <c r="T5" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>70</v>
       </c>
       <c r="T9" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="n">
         <v>25</v>
@@ -2219,10 +2219,10 @@
         <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T9" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2281,6 +2281,7 @@
 Spindelblomster
 Vedticka
 Vätteros
+Zontaggsvamp
 Linnea
 Mattlummer
 Nattskärra
@@ -2350,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2521,10 +2522,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2691,10 +2692,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2860,10 +2861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3020,10 +3021,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3181,10 +3182,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3337,10 +3338,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3491,10 +3492,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3629,10 +3630,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3761,10 +3762,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3884,10 +3885,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4008,10 +4009,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4128,10 +4129,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4239,10 +4240,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>403.2</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
         <v>25</v>
@@ -2397,10 +2397,10 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T10" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2474,7 +2474,8 @@
 Svartvit flugsnappare
 Trana
 Törnskata
-Fläcknycklar</t>
+Fläcknycklar
+Gullviva</t>
         </is>
       </c>
       <c r="W10">
@@ -2522,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2692,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2861,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3021,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3070,7 +3071,7 @@
         <v>54</v>
       </c>
       <c r="T14" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -3182,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3338,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3492,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3630,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3762,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3885,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4009,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4129,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4240,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4259,7 +4260,7 @@
         <v>102.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -4286,10 +4287,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -4299,6 +4300,7 @@
           <t>Sårläka
 Nästrot
 Tjäder
+Kopparödla
 Fläcknycklar</t>
         </is>
       </c>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>71</v>
       </c>
       <c r="T9" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>47</v>
       </c>
       <c r="T16" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>119</v>
       </c>
       <c r="T5" t="n">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>119</v>
       </c>
       <c r="T5" t="n">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>119</v>
       </c>
       <c r="T5" t="n">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>99</v>
       </c>
       <c r="T7" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
@@ -1389,10 +1389,10 @@
         <v>21</v>
       </c>
       <c r="S5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1472,6 +1472,7 @@
 Brandticka
 Bronshjon
 Dorcatoma dresdensis
+Fällmossa
 Granbarkgnagare
 Grovticka
 Grön sköldmossa
@@ -1569,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1784,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1806,7 +1807,7 @@
         <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>38</v>
@@ -1830,10 +1831,10 @@
         <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>706</v>
+        <v>729</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1901,6 +1902,7 @@
 Blåmossa
 Brandticka
 Bronshjon
+Fällmossa
 Granbarkgnagare
 Grovticka
 Grön sköldmossa
@@ -1990,10 +1992,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,10 +2175,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,10 +2353,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2523,10 +2525,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2693,10 +2695,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2862,10 +2864,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3022,10 +3024,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3183,10 +3185,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3339,10 +3341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3388,7 +3390,7 @@
         <v>47</v>
       </c>
       <c r="T16" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3493,10 +3495,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3631,10 +3633,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3763,10 +3765,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3886,10 +3888,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4010,10 +4012,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4130,10 +4132,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4241,10 +4243,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>120</v>
       </c>
       <c r="T4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>159.7</v>
       </c>
       <c r="J7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
@@ -1831,10 +1831,10 @@
         <v>18</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1928,6 +1928,7 @@
 Spillkråka
 Tallört (aggregat)
 Tjäder
+Tofsmes
 Gröngöling
 Havsörn
 Trana
@@ -1992,10 +1993,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2175,10 +2176,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2353,10 +2354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2525,10 +2526,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2695,10 +2696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2864,10 +2865,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3024,10 +3025,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3185,10 +3186,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3341,10 +3342,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3495,10 +3496,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3633,10 +3634,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3765,10 +3766,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3888,10 +3889,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4012,10 +4013,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4132,10 +4133,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4243,10 +4244,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1272</v>
+        <v>1292</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
